--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.5</v>
+        <v>4.06</v>
       </c>
       <c r="M59" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,22 +10619,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="M104" t="n">
-        <v>3.58</v>
+        <v>4.02</v>
       </c>
       <c r="N104" t="n">
-        <v>3.33</v>
+        <v>4.98</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M105" t="n">
-        <v>4.63</v>
+        <v>3.58</v>
       </c>
       <c r="N105" t="n">
-        <v>5.54</v>
+        <v>3.33</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AB105" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="M108" t="n">
-        <v>4.02</v>
+        <v>4.63</v>
       </c>
       <c r="N108" t="n">
-        <v>4.98</v>
+        <v>5.54</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15585,10 +15585,10 @@
         <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,73 +16010,73 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG131" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH131" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI131" s="3" t="n">
         <v>46081.5</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17370,10 +17370,10 @@
         <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD142" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,22 +18116,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,73 +18390,73 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V151" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X151" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD151" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI151" s="3" t="n">
         <v>46081.5</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,22 +19306,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,22 +24423,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26176,10 +26176,10 @@
         <v>0</v>
       </c>
       <c r="AC216" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD216" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26652,10 +26652,10 @@
         <v>0</v>
       </c>
       <c r="AC220" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD220" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE220" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,22 +27279,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,22 +27636,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,22 +30849,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33943,22 +33943,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34062,22 +34062,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L283" t="n">
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L284" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46081.33333333334</v>
+        <v>46081.35416666666</v>
       </c>
     </row>
     <row r="29">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46081.35416666666</v>
+        <v>46081.36458333334</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46081.36458333334</v>
+        <v>46081.375</v>
       </c>
     </row>
     <row r="33">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46081.375</v>
+        <v>46081.38541666666</v>
       </c>
     </row>
     <row r="37">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4902,27 +4902,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46081.38541666666</v>
+        <v>46081.39583333334</v>
       </c>
     </row>
     <row r="39">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46081.39583333334</v>
+        <v>46081.41666666666</v>
       </c>
     </row>
     <row r="50">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.06</v>
+        <v>2.5</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N59" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>46081.41666666666</v>
+        <v>46081.42708333334</v>
       </c>
     </row>
     <row r="67">
@@ -8353,12 +8353,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>46081.42708333334</v>
+        <v>46081.4375</v>
       </c>
     </row>
     <row r="68">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9781,27 +9781,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>46081.4375</v>
+        <v>46081.44791666666</v>
       </c>
     </row>
     <row r="80">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>46081.44791666666</v>
+        <v>46081.45833333334</v>
       </c>
     </row>
     <row r="82">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12518,27 +12518,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12628,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3" t="n">
-        <v>46081.45833333334</v>
+        <v>46081.46875</v>
       </c>
     </row>
     <row r="103">
@@ -12637,27 +12637,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12747,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="AI103" s="3" t="n">
-        <v>46081.46875</v>
+        <v>46081.47916666666</v>
       </c>
     </row>
     <row r="104">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="M104" t="n">
-        <v>4.02</v>
+        <v>4.63</v>
       </c>
       <c r="N104" t="n">
-        <v>4.98</v>
+        <v>5.54</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12919,10 +12919,10 @@
         <v>2.3</v>
       </c>
       <c r="M105" t="n">
-        <v>3.58</v>
+        <v>2.96</v>
       </c>
       <c r="N105" t="n">
-        <v>3.33</v>
+        <v>3.56</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="M106" t="n">
-        <v>2.96</v>
+        <v>4.47</v>
       </c>
       <c r="N106" t="n">
-        <v>3.56</v>
+        <v>6.91</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="M107" t="n">
-        <v>4.47</v>
+        <v>4.02</v>
       </c>
       <c r="N107" t="n">
-        <v>6.91</v>
+        <v>4.98</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB107" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13232,12 +13232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="3" t="n">
-        <v>46081.47916666666</v>
+        <v>46081.5</v>
       </c>
     </row>
     <row r="109">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13562,10 +13562,10 @@
         <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE110" t="n">
         <v>0</v>
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,73 +16010,73 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG131" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH131" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
         <v>46081.5</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17370,10 +17370,10 @@
         <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,73 +17914,73 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U147" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V147" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W147" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X147" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC147" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD147" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE147" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF147" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG147" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH147" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI147" s="3" t="n">
         <v>46081.5</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,22 +18116,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20015,12 +20015,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20125,7 +20125,7 @@
         <v>0</v>
       </c>
       <c r="AI165" s="3" t="n">
-        <v>46081.5</v>
+        <v>46081.51041666666</v>
       </c>
     </row>
     <row r="166">
@@ -20372,12 +20372,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20482,7 +20482,7 @@
         <v>0</v>
       </c>
       <c r="AI168" s="3" t="n">
-        <v>46081.51041666666</v>
+        <v>46081.52083333334</v>
       </c>
     </row>
     <row r="169">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21562,12 +21562,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21672,7 +21672,7 @@
         <v>0</v>
       </c>
       <c r="AI178" s="3" t="n">
-        <v>46081.52083333334</v>
+        <v>46081.54166666666</v>
       </c>
     </row>
     <row r="179">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22514,12 +22514,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22624,7 +22624,7 @@
         <v>0</v>
       </c>
       <c r="AI186" s="3" t="n">
-        <v>46081.54166666666</v>
+        <v>46081.55208333334</v>
       </c>
     </row>
     <row r="187">
@@ -22633,12 +22633,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22743,7 +22743,7 @@
         <v>0</v>
       </c>
       <c r="AI187" s="3" t="n">
-        <v>46081.55208333334</v>
+        <v>46081.5625</v>
       </c>
     </row>
     <row r="188">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23585,12 +23585,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23695,7 +23695,7 @@
         <v>0</v>
       </c>
       <c r="AI195" s="3" t="n">
-        <v>46081.5625</v>
+        <v>46081.57291666666</v>
       </c>
     </row>
     <row r="196">
@@ -23704,27 +23704,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23814,7 +23814,7 @@
         <v>0</v>
       </c>
       <c r="AI196" s="3" t="n">
-        <v>46081.57291666666</v>
+        <v>46081.58333333334</v>
       </c>
     </row>
     <row r="197">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25608,12 +25608,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25718,7 +25718,7 @@
         <v>0</v>
       </c>
       <c r="AI212" s="3" t="n">
-        <v>46081.58333333334</v>
+        <v>46081.59375</v>
       </c>
     </row>
     <row r="213">
@@ -25727,12 +25727,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25837,7 +25837,7 @@
         <v>0</v>
       </c>
       <c r="AI213" s="3" t="n">
-        <v>46081.59375</v>
+        <v>46081.60416666666</v>
       </c>
     </row>
     <row r="214">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26176,10 +26176,10 @@
         <v>0</v>
       </c>
       <c r="AC216" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD216" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26771,10 +26771,10 @@
         <v>0</v>
       </c>
       <c r="AC221" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD221" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE221" t="n">
         <v>0</v>
@@ -26798,12 +26798,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26908,7 +26908,7 @@
         <v>0</v>
       </c>
       <c r="AI222" s="3" t="n">
-        <v>46081.60416666666</v>
+        <v>46081.61458333334</v>
       </c>
     </row>
     <row r="223">
@@ -26917,12 +26917,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27027,7 +27027,7 @@
         <v>0</v>
       </c>
       <c r="AI223" s="3" t="n">
-        <v>46081.61458333334</v>
+        <v>46081.625</v>
       </c>
     </row>
     <row r="224">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,22 +30254,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,7 +32396,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -34062,22 +34062,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L283" t="n">
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L284" t="n">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G289" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,22 +10857,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="M103" t="n">
-        <v>3.58</v>
+        <v>4.47</v>
       </c>
       <c r="N103" t="n">
-        <v>3.33</v>
+        <v>6.91</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="M105" t="n">
-        <v>2.96</v>
+        <v>4.02</v>
       </c>
       <c r="N105" t="n">
-        <v>3.56</v>
+        <v>4.98</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="M106" t="n">
-        <v>4.47</v>
+        <v>2.96</v>
       </c>
       <c r="N106" t="n">
-        <v>6.91</v>
+        <v>3.56</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M107" t="n">
-        <v>4.02</v>
+        <v>3.58</v>
       </c>
       <c r="N107" t="n">
-        <v>4.98</v>
+        <v>3.33</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13562,10 +13562,10 @@
         <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,73 +17200,73 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W141" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X141" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC141" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD141" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE141" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF141" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG141" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH141" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI141" s="3" t="n">
         <v>46081.5</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>4.62</v>
+        <v>1.41</v>
       </c>
       <c r="M145" t="n">
-        <v>3.88</v>
+        <v>5.33</v>
       </c>
       <c r="N145" t="n">
-        <v>1.85</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,16 +17721,16 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD145" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,73 +17914,73 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U147" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X147" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD147" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF147" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG147" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH147" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI147" s="3" t="n">
         <v>46081.5</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23709,22 +23709,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26295,10 +26295,10 @@
         <v>0</v>
       </c>
       <c r="AC217" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD217" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE217" t="n">
         <v>0</v>
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>4.17</v>
+        <v>2.2</v>
       </c>
       <c r="M221" t="n">
-        <v>4.37</v>
+        <v>3.08</v>
       </c>
       <c r="N221" t="n">
-        <v>1.83</v>
+        <v>3.47</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26771,10 +26771,10 @@
         <v>0</v>
       </c>
       <c r="AC221" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD221" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE221" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27398,22 +27398,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,22 +27636,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,22 +30492,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33943,22 +33943,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,22 +10857,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M103" t="n">
-        <v>4.47</v>
+        <v>4.63</v>
       </c>
       <c r="N103" t="n">
-        <v>6.91</v>
+        <v>5.54</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB103" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="M104" t="n">
-        <v>4.63</v>
+        <v>4.47</v>
       </c>
       <c r="N104" t="n">
-        <v>5.54</v>
+        <v>6.91</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M105" t="n">
-        <v>4.02</v>
+        <v>3.58</v>
       </c>
       <c r="N105" t="n">
-        <v>4.98</v>
+        <v>3.33</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AB105" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="M107" t="n">
-        <v>3.58</v>
+        <v>4.02</v>
       </c>
       <c r="N107" t="n">
-        <v>3.33</v>
+        <v>4.98</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,73 +17200,73 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="M141" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="N141" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="O141" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD141" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF141" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG141" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH141" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
         <v>46081.5</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17489,10 +17489,10 @@
         <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17727,10 +17727,10 @@
         <v>0</v>
       </c>
       <c r="AC145" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD145" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,73 +18152,73 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="M149" t="n">
-        <v>4.27</v>
+        <v>3.9</v>
       </c>
       <c r="N149" t="n">
-        <v>5.33</v>
+        <v>4.8</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S149" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T149" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U149" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W149" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X149" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y149" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA149" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE149" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB149" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE149" t="n">
-        <v>0</v>
-      </c>
       <c r="AF149" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG149" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH149" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI149" s="3" t="n">
         <v>46081.5</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB184" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,22 +24185,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26295,10 +26295,10 @@
         <v>0</v>
       </c>
       <c r="AC217" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD217" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26652,10 +26652,10 @@
         <v>0</v>
       </c>
       <c r="AC220" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD220" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,22 +30492,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33943,22 +33943,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L284" t="n">
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L285" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="M103" t="n">
-        <v>4.63</v>
+        <v>4.47</v>
       </c>
       <c r="N103" t="n">
-        <v>5.54</v>
+        <v>6.91</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="M104" t="n">
-        <v>4.47</v>
+        <v>3.58</v>
       </c>
       <c r="N104" t="n">
-        <v>6.91</v>
+        <v>3.33</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AB104" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M105" t="n">
-        <v>3.58</v>
+        <v>4.63</v>
       </c>
       <c r="N105" t="n">
-        <v>3.33</v>
+        <v>5.54</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17489,10 +17489,10 @@
         <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,73 +18152,73 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG149" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH149" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI149" s="3" t="n">
         <v>46081.5</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,73 +19580,73 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T161" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U161" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V161" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W161" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X161" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z161" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD161" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG161" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH161" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI161" s="3" t="n">
         <v>46081.5</v>
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,22 +24185,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26414,10 +26414,10 @@
         <v>0</v>
       </c>
       <c r="AC218" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD218" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26652,10 +26652,10 @@
         <v>0</v>
       </c>
       <c r="AC220" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD220" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE220" t="n">
         <v>0</v>
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26922,22 +26922,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27398,22 +27398,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,22 +30254,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33943,22 +33943,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34062,22 +34062,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L284" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L285" t="n">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="M103" t="n">
-        <v>4.47</v>
+        <v>4.02</v>
       </c>
       <c r="N103" t="n">
-        <v>6.91</v>
+        <v>4.98</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB103" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M104" t="n">
-        <v>3.58</v>
+        <v>4.63</v>
       </c>
       <c r="N104" t="n">
-        <v>3.33</v>
+        <v>5.54</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M105" t="n">
-        <v>4.63</v>
+        <v>3.58</v>
       </c>
       <c r="N105" t="n">
-        <v>5.54</v>
+        <v>3.33</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AB105" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="M107" t="n">
-        <v>4.02</v>
+        <v>4.47</v>
       </c>
       <c r="N107" t="n">
-        <v>4.98</v>
+        <v>6.91</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,73 +14344,73 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG117" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI117" s="3" t="n">
         <v>46081.5</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,22 +17997,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>4.62</v>
+        <v>3.94</v>
       </c>
       <c r="M155" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="N155" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="M158" t="n">
-        <v>4.27</v>
+        <v>3.41</v>
       </c>
       <c r="N158" t="n">
-        <v>5.33</v>
+        <v>3.42</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,73 +19580,73 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.6</v>
+        <v>3.03</v>
       </c>
       <c r="M161" t="n">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="N161" t="n">
-        <v>4.8</v>
+        <v>2.29</v>
       </c>
       <c r="O161" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U161" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V161" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X161" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AC161" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH161" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI161" s="3" t="n">
         <v>46081.5</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25105,10 +25105,10 @@
         <v>0</v>
       </c>
       <c r="AC207" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD207" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26057,10 +26057,10 @@
         <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD215" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE215" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26414,10 +26414,10 @@
         <v>0</v>
       </c>
       <c r="AC218" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE218" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26922,22 +26922,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27279,22 +27279,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L283" t="n">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L284" t="n">
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.66</v>
+        <v>1.93</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.39</v>
+        <v>3.65</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.99</v>
+        <v>2.66</v>
       </c>
       <c r="M41" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>4.02</v>
+        <v>2.39</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>4.23</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="M105" t="n">
-        <v>3.58</v>
+        <v>4.47</v>
       </c>
       <c r="N105" t="n">
-        <v>3.33</v>
+        <v>6.91</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="M107" t="n">
-        <v>4.47</v>
+        <v>3.58</v>
       </c>
       <c r="N107" t="n">
-        <v>6.91</v>
+        <v>3.33</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AB107" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="M113" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="N113" t="n">
-        <v>2.87</v>
+        <v>5.58</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="M114" t="n">
         <v>3.28</v>
       </c>
       <c r="N114" t="n">
-        <v>3.26</v>
+        <v>2.87</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,73 +14344,73 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="M117" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N117" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="O117" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U117" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V117" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
         <v>46081.5</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.94</v>
+        <v>1.45</v>
       </c>
       <c r="M120" t="n">
-        <v>3.02</v>
+        <v>4.35</v>
       </c>
       <c r="N120" t="n">
-        <v>2.34</v>
+        <v>6.75</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.69</v>
+        <v>3.94</v>
       </c>
       <c r="M130" t="n">
         <v>3.78</v>
       </c>
       <c r="N130" t="n">
-        <v>4.75</v>
+        <v>1.82</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.7</v>
+        <v>4.62</v>
       </c>
       <c r="M135" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="N135" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.3</v>
+        <v>3.03</v>
       </c>
       <c r="M139" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N139" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,73 +17200,73 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>4.61</v>
+        <v>1.6</v>
       </c>
       <c r="M141" t="n">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="N141" t="n">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W141" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X141" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AC141" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD141" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE141" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF141" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG141" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH141" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI141" s="3" t="n">
         <v>46081.5</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>4.62</v>
+        <v>1.78</v>
       </c>
       <c r="M147" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="N147" t="n">
-        <v>1.85</v>
+        <v>4.28</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,22 +17997,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>5.53</v>
+        <v>2</v>
       </c>
       <c r="M149" t="n">
-        <v>4.39</v>
+        <v>3.45</v>
       </c>
       <c r="N149" t="n">
-        <v>1.47</v>
+        <v>3.51</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="M150" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="N150" t="n">
-        <v>5.58</v>
+        <v>4.75</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,16 +18316,16 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB150" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC150" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD150" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE150" t="n">
         <v>0</v>
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="M151" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="N151" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="M152" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="N152" t="n">
-        <v>5.33</v>
+        <v>7.38</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="M154" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N154" t="n">
-        <v>3.54</v>
+        <v>3.09</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>3.94</v>
+        <v>2.2</v>
       </c>
       <c r="M155" t="n">
-        <v>3.78</v>
+        <v>3.28</v>
       </c>
       <c r="N155" t="n">
-        <v>1.82</v>
+        <v>3.26</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="M157" t="n">
-        <v>3.84</v>
+        <v>4.27</v>
       </c>
       <c r="N157" t="n">
-        <v>5.17</v>
+        <v>5.33</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.84</v>
+        <v>1.41</v>
       </c>
       <c r="M159" t="n">
-        <v>3.25</v>
+        <v>5.33</v>
       </c>
       <c r="N159" t="n">
-        <v>2.45</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.41</v>
+        <v>4.61</v>
       </c>
       <c r="M160" t="n">
-        <v>5.33</v>
+        <v>3.62</v>
       </c>
       <c r="N160" t="n">
-        <v>8.300000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,16 +19506,16 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC160" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>3.03</v>
+        <v>1.66</v>
       </c>
       <c r="M161" t="n">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="N161" t="n">
-        <v>2.29</v>
+        <v>4.78</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="M163" t="n">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="N163" t="n">
-        <v>2.47</v>
+        <v>3.54</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24153,10 +24153,10 @@
         <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD199" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25105,10 +25105,10 @@
         <v>0</v>
       </c>
       <c r="AC207" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD207" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26057,10 +26057,10 @@
         <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD215" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26533,10 +26533,10 @@
         <v>0</v>
       </c>
       <c r="AC219" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD219" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -27041,22 +27041,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,22 +27279,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>4.23</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.66</v>
+        <v>1.93</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.39</v>
+        <v>3.65</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.66</v>
+        <v>2.9</v>
       </c>
       <c r="N42" t="n">
-        <v>4.23</v>
+        <v>2.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="M45" t="n">
-        <v>3.78</v>
+        <v>3.48</v>
       </c>
       <c r="N45" t="n">
-        <v>4.02</v>
+        <v>2.31</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.5</v>
+        <v>4.06</v>
       </c>
       <c r="M52" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,22 +10619,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="M103" t="n">
-        <v>4.02</v>
+        <v>4.47</v>
       </c>
       <c r="N103" t="n">
-        <v>4.98</v>
+        <v>6.91</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M104" t="n">
-        <v>4.63</v>
+        <v>3.58</v>
       </c>
       <c r="N104" t="n">
-        <v>5.54</v>
+        <v>3.33</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="M105" t="n">
-        <v>4.47</v>
+        <v>4.02</v>
       </c>
       <c r="N105" t="n">
-        <v>6.91</v>
+        <v>4.98</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB105" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M107" t="n">
-        <v>3.58</v>
+        <v>4.63</v>
       </c>
       <c r="N107" t="n">
-        <v>3.33</v>
+        <v>5.54</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.42</v>
+        <v>3.03</v>
       </c>
       <c r="M114" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="N114" t="n">
-        <v>2.87</v>
+        <v>2.29</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.26</v>
+        <v>1.66</v>
       </c>
       <c r="M119" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="N119" t="n">
-        <v>2.22</v>
+        <v>4.78</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M120" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="N120" t="n">
-        <v>6.75</v>
+        <v>7.38</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.63</v>
+        <v>2.94</v>
       </c>
       <c r="M128" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="N128" t="n">
-        <v>5.17</v>
+        <v>2.34</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.94</v>
+        <v>3.26</v>
       </c>
       <c r="M130" t="n">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="N130" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3.03</v>
+        <v>3.37</v>
       </c>
       <c r="M139" t="n">
         <v>3.32</v>
       </c>
       <c r="N139" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,73 +17200,73 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="M141" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="N141" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="O141" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD141" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF141" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG141" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH141" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
         <v>46081.5</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="M142" t="n">
         <v>3.62</v>
       </c>
-      <c r="M142" t="n">
-        <v>3.44</v>
-      </c>
       <c r="N142" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,22 +17640,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.9</v>
+        <v>1.69</v>
       </c>
       <c r="M146" t="n">
-        <v>3.11</v>
+        <v>3.78</v>
       </c>
       <c r="N146" t="n">
-        <v>2.47</v>
+        <v>4.75</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,16 +17840,16 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC146" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD146" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,16 +18316,16 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC150" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD150" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.41</v>
+        <v>2.9</v>
       </c>
       <c r="M152" t="n">
-        <v>4.5</v>
+        <v>3.11</v>
       </c>
       <c r="N152" t="n">
-        <v>7.38</v>
+        <v>2.47</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="M155" t="n">
-        <v>3.28</v>
+        <v>3.82</v>
       </c>
       <c r="N155" t="n">
-        <v>3.26</v>
+        <v>4.67</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="M156" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N156" t="n">
-        <v>5</v>
+        <v>3.09</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="M157" t="n">
-        <v>4.27</v>
+        <v>5.33</v>
       </c>
       <c r="N157" t="n">
-        <v>5.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="M159" t="n">
-        <v>5.33</v>
+        <v>3.5</v>
       </c>
       <c r="N159" t="n">
-        <v>8.300000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,73 +19461,73 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>4.61</v>
+        <v>1.6</v>
       </c>
       <c r="M160" t="n">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="N160" t="n">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="O160" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S160" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T160" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U160" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V160" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W160" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X160" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG160" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH160" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI160" s="3" t="n">
         <v>46081.5</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>5.53</v>
+        <v>2.3</v>
       </c>
       <c r="M164" t="n">
-        <v>4.39</v>
+        <v>3.25</v>
       </c>
       <c r="N164" t="n">
-        <v>1.47</v>
+        <v>2.88</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24153,10 +24153,10 @@
         <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD199" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25105,10 +25105,10 @@
         <v>0</v>
       </c>
       <c r="AC207" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD207" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25938,10 +25938,10 @@
         <v>0</v>
       </c>
       <c r="AC214" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD214" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26533,10 +26533,10 @@
         <v>0</v>
       </c>
       <c r="AC219" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD219" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,22 +27041,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.48</v>
+        <v>3.91</v>
       </c>
       <c r="M225" t="n">
-        <v>4.62</v>
+        <v>3.44</v>
       </c>
       <c r="N225" t="n">
-        <v>8</v>
+        <v>1.92</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AB225" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27517,22 +27517,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,7 +32396,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L283" t="n">
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L285" t="n">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="M38" t="n">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="N38" t="n">
-        <v>4.23</v>
+        <v>4.02</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.93</v>
+        <v>2.66</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>3.65</v>
+        <v>2.39</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.5</v>
+        <v>4.06</v>
       </c>
       <c r="M51" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,22 +10619,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,22 +10857,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M103" t="n">
-        <v>4.47</v>
+        <v>4.63</v>
       </c>
       <c r="N103" t="n">
-        <v>6.91</v>
+        <v>5.54</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB103" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="M104" t="n">
-        <v>3.58</v>
+        <v>4.47</v>
       </c>
       <c r="N104" t="n">
-        <v>3.33</v>
+        <v>6.91</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13038,10 +13038,10 @@
         <v>2.3</v>
       </c>
       <c r="M106" t="n">
-        <v>2.96</v>
+        <v>3.58</v>
       </c>
       <c r="N106" t="n">
-        <v>3.56</v>
+        <v>3.33</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M107" t="n">
-        <v>4.63</v>
+        <v>2.96</v>
       </c>
       <c r="N107" t="n">
-        <v>5.54</v>
+        <v>3.56</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>5.53</v>
+        <v>2.94</v>
       </c>
       <c r="M108" t="n">
-        <v>4.39</v>
+        <v>3.02</v>
       </c>
       <c r="N108" t="n">
-        <v>1.47</v>
+        <v>2.34</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.03</v>
+        <v>3.37</v>
       </c>
       <c r="M114" t="n">
         <v>3.32</v>
       </c>
       <c r="N114" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="M121" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="N121" t="n">
-        <v>5.33</v>
+        <v>7.38</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.94</v>
+        <v>5.53</v>
       </c>
       <c r="M128" t="n">
-        <v>3.02</v>
+        <v>4.39</v>
       </c>
       <c r="N128" t="n">
-        <v>2.34</v>
+        <v>1.47</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.26</v>
+        <v>1.69</v>
       </c>
       <c r="M130" t="n">
-        <v>3.52</v>
+        <v>3.78</v>
       </c>
       <c r="N130" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,16 +15936,16 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.45</v>
+        <v>3.03</v>
       </c>
       <c r="M131" t="n">
-        <v>4.35</v>
+        <v>3.32</v>
       </c>
       <c r="N131" t="n">
-        <v>6.75</v>
+        <v>2.29</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,73 +16843,73 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>3.26</v>
+        <v>1.6</v>
       </c>
       <c r="M138" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="N138" t="n">
-        <v>2.22</v>
+        <v>4.8</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V138" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W138" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z138" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC138" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD138" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG138" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH138" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI138" s="3" t="n">
         <v>46081.5</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3.37</v>
+        <v>1.69</v>
       </c>
       <c r="M139" t="n">
-        <v>3.32</v>
+        <v>4.27</v>
       </c>
       <c r="N139" t="n">
-        <v>2.13</v>
+        <v>5.33</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.78</v>
+        <v>4.62</v>
       </c>
       <c r="M140" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="N140" t="n">
-        <v>4.28</v>
+        <v>1.85</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="M141" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N141" t="n">
-        <v>3.54</v>
+        <v>5</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>4.61</v>
+        <v>2.84</v>
       </c>
       <c r="M142" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="N142" t="n">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="M143" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N143" t="n">
-        <v>2.45</v>
+        <v>3.09</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,22 +17640,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,16 +17840,16 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD146" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.66</v>
+        <v>2.42</v>
       </c>
       <c r="M155" t="n">
-        <v>3.82</v>
+        <v>3.28</v>
       </c>
       <c r="N155" t="n">
-        <v>4.67</v>
+        <v>2.87</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="M156" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N156" t="n">
-        <v>3.09</v>
+        <v>3.7</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.41</v>
+        <v>3.94</v>
       </c>
       <c r="M157" t="n">
-        <v>5.33</v>
+        <v>3.78</v>
       </c>
       <c r="N157" t="n">
-        <v>8.300000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>4.62</v>
+        <v>1.63</v>
       </c>
       <c r="M158" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="N158" t="n">
-        <v>1.85</v>
+        <v>5.17</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="M159" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="N159" t="n">
-        <v>3.7</v>
+        <v>6.75</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,73 +19461,73 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="M160" t="n">
-        <v>3.9</v>
+        <v>3.41</v>
       </c>
       <c r="N160" t="n">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="O160" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V160" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X160" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC160" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH160" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI160" s="3" t="n">
         <v>46081.5</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="M162" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N162" t="n">
-        <v>5</v>
+        <v>3.54</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19869,10 +19869,10 @@
         <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD163" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24272,10 +24272,10 @@
         <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD200" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25105,10 +25105,10 @@
         <v>0</v>
       </c>
       <c r="AC207" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD207" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27398,22 +27398,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27517,22 +27517,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30492,22 +30492,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,22 +30849,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L283" t="n">
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L285" t="n">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.99</v>
+        <v>2.31</v>
       </c>
       <c r="M38" t="n">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="N38" t="n">
-        <v>4.02</v>
+        <v>2.84</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.66</v>
+        <v>2.9</v>
       </c>
       <c r="N40" t="n">
-        <v>4.23</v>
+        <v>2.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="N41" t="n">
-        <v>2.39</v>
+        <v>2.78</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="N48" t="n">
-        <v>3.65</v>
+        <v>2.31</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="M59" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,22 +10857,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M103" t="n">
-        <v>4.63</v>
+        <v>2.96</v>
       </c>
       <c r="N103" t="n">
-        <v>5.54</v>
+        <v>3.56</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M107" t="n">
-        <v>2.96</v>
+        <v>4.63</v>
       </c>
       <c r="N107" t="n">
-        <v>3.56</v>
+        <v>5.54</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>3.26</v>
+        <v>1.33</v>
       </c>
       <c r="M113" t="n">
-        <v>3.22</v>
+        <v>4.8</v>
       </c>
       <c r="N113" t="n">
-        <v>2.22</v>
+        <v>8.1</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.78</v>
+        <v>3.03</v>
       </c>
       <c r="M117" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N117" t="n">
-        <v>4.28</v>
+        <v>2.29</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>5.53</v>
+        <v>1.69</v>
       </c>
       <c r="M128" t="n">
-        <v>4.39</v>
+        <v>3.78</v>
       </c>
       <c r="N128" t="n">
-        <v>1.47</v>
+        <v>4.75</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,16 +15698,16 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD128" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,73 +15891,73 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="M130" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="N130" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U130" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V130" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W130" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC130" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD130" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG130" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH130" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI130" s="3" t="n">
         <v>46081.5</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.03</v>
+        <v>4.62</v>
       </c>
       <c r="M131" t="n">
-        <v>3.32</v>
+        <v>3.88</v>
       </c>
       <c r="N131" t="n">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="M137" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N137" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,73 +16843,73 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M138" t="n">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
       <c r="N138" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="O138" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AB138" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC138" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH138" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI138" s="3" t="n">
         <v>46081.5</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="M139" t="n">
-        <v>4.27</v>
+        <v>3.95</v>
       </c>
       <c r="N139" t="n">
-        <v>5.33</v>
+        <v>5.17</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="M142" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N142" t="n">
-        <v>2.45</v>
+        <v>4.28</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="M143" t="n">
         <v>3.3</v>
       </c>
       <c r="N143" t="n">
-        <v>3.09</v>
+        <v>2.55</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="M144" t="n">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="N144" t="n">
-        <v>4.67</v>
+        <v>5.57</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,61 +17676,61 @@
         </is>
       </c>
       <c r="L145" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M145" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N145" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC145" t="n">
         <v>2.3</v>
       </c>
-      <c r="M145" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N145" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" t="n">
-        <v>0</v>
-      </c>
-      <c r="V145" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" t="n">
-        <v>0</v>
-      </c>
-      <c r="X145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB145" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC145" t="n">
-        <v>0</v>
-      </c>
       <c r="AD145" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>4.61</v>
+        <v>2.35</v>
       </c>
       <c r="M147" t="n">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="N147" t="n">
-        <v>1.74</v>
+        <v>2.86</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="M150" t="n">
-        <v>3.28</v>
+        <v>3.66</v>
       </c>
       <c r="N150" t="n">
-        <v>3.26</v>
+        <v>3.51</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>3.26</v>
+        <v>1.63</v>
       </c>
       <c r="M151" t="n">
-        <v>3.52</v>
+        <v>3.84</v>
       </c>
       <c r="N151" t="n">
-        <v>2.1</v>
+        <v>5.17</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="M155" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="N155" t="n">
-        <v>2.87</v>
+        <v>2.34</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="M156" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N156" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3.94</v>
+        <v>2.84</v>
       </c>
       <c r="M157" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="N157" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="M158" t="n">
-        <v>3.84</v>
+        <v>4.27</v>
       </c>
       <c r="N158" t="n">
-        <v>5.17</v>
+        <v>5.33</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,22 +19306,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="M160" t="n">
-        <v>3.41</v>
+        <v>4.05</v>
       </c>
       <c r="N160" t="n">
-        <v>3.42</v>
+        <v>4.74</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="M162" t="n">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="N162" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB181" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24272,10 +24272,10 @@
         <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD200" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,22 +24423,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25581,10 +25581,10 @@
         <v>0</v>
       </c>
       <c r="AC211" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD211" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE211" t="n">
         <v>0</v>
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>4.17</v>
+        <v>2.2</v>
       </c>
       <c r="M214" t="n">
-        <v>4.37</v>
+        <v>3.08</v>
       </c>
       <c r="N214" t="n">
-        <v>1.83</v>
+        <v>3.47</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25938,10 +25938,10 @@
         <v>0</v>
       </c>
       <c r="AC214" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD214" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>3.49</v>
+        <v>4.17</v>
       </c>
       <c r="M215" t="n">
-        <v>3.3</v>
+        <v>4.37</v>
       </c>
       <c r="N215" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26057,10 +26057,10 @@
         <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD215" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="M218" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N218" t="n">
-        <v>3.68</v>
+        <v>4.56</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27160,22 +27160,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27398,22 +27398,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.48</v>
+        <v>3.35</v>
       </c>
       <c r="M229" t="n">
-        <v>4.62</v>
+        <v>3.34</v>
       </c>
       <c r="N229" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28148,13 +28148,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28267,13 +28267,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30097,10 +30097,10 @@
         <v>0</v>
       </c>
       <c r="AA249" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB249" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC249" t="n">
         <v>0</v>
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30849,22 +30849,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB257" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33072,10 +33072,10 @@
         <v>0</v>
       </c>
       <c r="AA274" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB274" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34574,13 +34574,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -34693,13 +34693,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -34738,10 +34738,10 @@
         <v>0</v>
       </c>
       <c r="AA288" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB288" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC288" t="n">
         <v>0</v>
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34812,13 +34812,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M289" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -34857,10 +34857,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB289" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC289" t="n">
         <v>0</v>
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -34931,13 +34931,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -35169,13 +35169,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M292" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -35214,10 +35214,10 @@
         <v>0</v>
       </c>
       <c r="AA292" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB292" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC292" t="n">
         <v>0</v>

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="M43" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>4.02</v>
+        <v>3.65</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="N44" t="n">
-        <v>3.65</v>
+        <v>2.78</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="M45" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="N45" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.88</v>
+        <v>1.69</v>
       </c>
       <c r="M46" t="n">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="N46" t="n">
-        <v>2.31</v>
+        <v>4.23</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.69</v>
+        <v>2.21</v>
       </c>
       <c r="M47" t="n">
-        <v>3.66</v>
+        <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>4.23</v>
+        <v>3.23</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="M50" t="n">
-        <v>2.9</v>
+        <v>3.54</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>3.46</v>
+        <v>2.65</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M96" t="n">
-        <v>3.85</v>
+        <v>4.63</v>
       </c>
       <c r="N96" t="n">
-        <v>6.28</v>
+        <v>9.25</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.99</v>
+        <v>2.18</v>
       </c>
       <c r="M98" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N98" t="n">
-        <v>2.12</v>
+        <v>3.17</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="M109" t="n">
-        <v>2.96</v>
+        <v>4.02</v>
       </c>
       <c r="N109" t="n">
-        <v>3.56</v>
+        <v>4.98</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M112" t="n">
-        <v>4.02</v>
+        <v>2.96</v>
       </c>
       <c r="N112" t="n">
-        <v>4.98</v>
+        <v>3.56</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,14 +13868,14 @@
         </is>
       </c>
       <c r="L113" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="M113" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="N113" t="n">
         <v>1.85</v>
       </c>
-      <c r="M113" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N113" t="n">
-        <v>3.7</v>
-      </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.37</v>
+        <v>2.04</v>
       </c>
       <c r="M114" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N114" t="n">
-        <v>2.13</v>
+        <v>3.42</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="M117" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="N117" t="n">
-        <v>4.75</v>
+        <v>5.17</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,16 +14389,16 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.62</v>
+        <v>1.66</v>
       </c>
       <c r="M121" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="N121" t="n">
-        <v>2</v>
+        <v>4.78</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="M123" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>8.1</v>
+        <v>4.28</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="M124" t="n">
-        <v>4.27</v>
+        <v>3.64</v>
       </c>
       <c r="N124" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="M125" t="n">
         <v>3.28</v>
       </c>
       <c r="N125" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.45</v>
+        <v>3</v>
       </c>
       <c r="M126" t="n">
-        <v>4.35</v>
+        <v>3.26</v>
       </c>
       <c r="N126" t="n">
-        <v>6.75</v>
+        <v>2.34</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="M127" t="n">
-        <v>3.84</v>
+        <v>5.33</v>
       </c>
       <c r="N127" t="n">
-        <v>5.17</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,16 +15579,16 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15704,10 +15704,10 @@
         <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,16 +16293,16 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD133" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>5.53</v>
+        <v>1.64</v>
       </c>
       <c r="M134" t="n">
-        <v>4.39</v>
+        <v>4.05</v>
       </c>
       <c r="N134" t="n">
-        <v>1.47</v>
+        <v>4.74</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>4.62</v>
+        <v>2.2</v>
       </c>
       <c r="M136" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="N136" t="n">
-        <v>1.85</v>
+        <v>3.26</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3.26</v>
+        <v>1.41</v>
       </c>
       <c r="M139" t="n">
-        <v>3.52</v>
+        <v>4.5</v>
       </c>
       <c r="N139" t="n">
-        <v>2.1</v>
+        <v>7.38</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="M140" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="N140" t="n">
-        <v>7.38</v>
+        <v>8.1</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,73 +17319,73 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="M142" t="n">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="N142" t="n">
-        <v>4.8</v>
+        <v>3.51</v>
       </c>
       <c r="O142" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH142" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI142" s="3" t="n">
         <v>46081.5</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,22 +17521,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.94</v>
+        <v>1.54</v>
       </c>
       <c r="M147" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="N147" t="n">
-        <v>2.34</v>
+        <v>5.58</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.03</v>
+        <v>3.62</v>
       </c>
       <c r="M148" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="N148" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,7 +18078,7 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB148" t="n">
         <v>1.82</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="M149" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N149" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,16 +18197,16 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC149" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD149" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE149" t="n">
         <v>0</v>
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>3.26</v>
+        <v>2.42</v>
       </c>
       <c r="M150" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="N150" t="n">
-        <v>2.22</v>
+        <v>2.87</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="M151" t="n">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="N151" t="n">
-        <v>5.17</v>
+        <v>6.75</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M152" t="n">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N152" t="n">
-        <v>4.74</v>
+        <v>5.17</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AB152" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,16 +18673,16 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD153" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.78</v>
+        <v>2.84</v>
       </c>
       <c r="M155" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N155" t="n">
-        <v>4.28</v>
+        <v>2.45</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,73 +19104,73 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M157" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N157" t="n">
-        <v>3.51</v>
+        <v>4.8</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U157" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V157" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W157" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X157" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI157" s="3" t="n">
         <v>46081.5</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="M158" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N158" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="M159" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="N159" t="n">
-        <v>5.58</v>
+        <v>4.67</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="M160" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N160" t="n">
-        <v>4.78</v>
+        <v>3.09</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="M161" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="N161" t="n">
-        <v>3.51</v>
+        <v>5</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.9</v>
+        <v>5.53</v>
       </c>
       <c r="M164" t="n">
-        <v>3.11</v>
+        <v>4.39</v>
       </c>
       <c r="N164" t="n">
-        <v>2.47</v>
+        <v>1.47</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.35</v>
+        <v>4.61</v>
       </c>
       <c r="M167" t="n">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="N167" t="n">
-        <v>2.86</v>
+        <v>1.74</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.24</v>
+        <v>3.26</v>
       </c>
       <c r="M168" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="N168" t="n">
-        <v>3.09</v>
+        <v>2.1</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB168" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.66</v>
+        <v>3.94</v>
       </c>
       <c r="M169" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="N169" t="n">
-        <v>4.67</v>
+        <v>1.82</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.87</v>
+        <v>11.8</v>
       </c>
       <c r="M179" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="N179" t="n">
-        <v>3.93</v>
+        <v>1.25</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.22</v>
+        <v>1.18</v>
       </c>
       <c r="M183" t="n">
-        <v>2.75</v>
+        <v>6.6</v>
       </c>
       <c r="N183" t="n">
-        <v>3.83</v>
+        <v>14.1</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,22 +24542,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,22 +25851,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.19</v>
+        <v>3.49</v>
       </c>
       <c r="M218" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="N218" t="n">
-        <v>3.41</v>
+        <v>2.12</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="M219" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N219" t="n">
-        <v>4.56</v>
+        <v>3.68</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="M224" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N224" t="n">
-        <v>3.68</v>
+        <v>4.56</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>3.49</v>
+        <v>2.19</v>
       </c>
       <c r="M225" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N225" t="n">
-        <v>2.12</v>
+        <v>3.41</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27517,22 +27517,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27755,22 +27755,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27836,10 +27836,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB230" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>1.48</v>
+        <v>2.88</v>
       </c>
       <c r="M231" t="n">
-        <v>4.62</v>
+        <v>2.93</v>
       </c>
       <c r="N231" t="n">
-        <v>8</v>
+        <v>2.43</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB231" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC231" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>2.88</v>
+        <v>1.48</v>
       </c>
       <c r="M232" t="n">
-        <v>2.93</v>
+        <v>4.62</v>
       </c>
       <c r="N232" t="n">
-        <v>2.43</v>
+        <v>8</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28074,10 +28074,10 @@
         <v>0</v>
       </c>
       <c r="AA232" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB232" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28148,13 +28148,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28267,13 +28267,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -28312,10 +28312,10 @@
         <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB234" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC234" t="n">
         <v>0</v>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28624,13 +28624,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29457,13 +29457,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30409,13 +30409,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -30454,10 +30454,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB252" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N253" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30573,10 +30573,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB253" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,22 +30849,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="M257" t="n">
-        <v>3.93</v>
+        <v>4.32</v>
       </c>
       <c r="N257" t="n">
-        <v>4.12</v>
+        <v>4.4</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB257" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31920,22 +31920,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,22 +32039,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32432,13 +32432,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,22 +32872,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33622,13 +33622,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -33667,10 +33667,10 @@
         <v>0</v>
       </c>
       <c r="AA279" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB279" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC279" t="n">
         <v>0</v>
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33786,10 +33786,10 @@
         <v>0</v>
       </c>
       <c r="AA280" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB280" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC280" t="n">
         <v>0</v>
@@ -33824,22 +33824,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33943,22 +33943,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34538,22 +34538,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34570,7 +34570,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L287" t="n">
@@ -34657,22 +34657,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L288" t="n">
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35050,13 +35050,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35169,13 +35169,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M292" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35288,13 +35288,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>3.63</v>
+        <v>2.43</v>
       </c>
       <c r="M293" t="n">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="N293" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -35333,10 +35333,10 @@
         <v>0</v>
       </c>
       <c r="AA293" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB293" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC293" t="n">
         <v>0</v>
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.43</v>
+        <v>3.63</v>
       </c>
       <c r="M295" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="N295" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35571,10 +35571,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>

--- a/jogos_2026-02-28.xlsx
+++ b/jogos_2026-02-28.xlsx
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="M35" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>4.02</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="M42" t="n">
-        <v>2.9</v>
+        <v>3.36</v>
       </c>
       <c r="N42" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.41</v>
+        <v>1.69</v>
       </c>
       <c r="M44" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="N44" t="n">
-        <v>2.78</v>
+        <v>4.23</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="M46" t="n">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>4.23</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="M47" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="N47" t="n">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB47" t="n">
         <v>2</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,14 +6371,14 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N50" t="n">
         <v>2.31</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.84</v>
-      </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB50" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="M51" t="n">
-        <v>3.78</v>
+        <v>3.28</v>
       </c>
       <c r="N51" t="n">
-        <v>4.02</v>
+        <v>3.23</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.18</v>
+        <v>2.65</v>
       </c>
       <c r="M55" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="N55" t="n">
-        <v>13.9</v>
+        <v>2.65</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.45</v>
+        <v>3.99</v>
       </c>
       <c r="M96" t="n">
-        <v>4.63</v>
+        <v>2.9</v>
       </c>
       <c r="N96" t="n">
-        <v>9.25</v>
+        <v>2.12</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="M108" t="n">
-        <v>4.63</v>
+        <v>4.47</v>
       </c>
       <c r="N108" t="n">
-        <v>5.54</v>
+        <v>6.91</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M109" t="n">
-        <v>4.02</v>
+        <v>3.58</v>
       </c>
       <c r="N109" t="n">
-        <v>4.98</v>
+        <v>3.33</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AB109" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="M110" t="n">
-        <v>3.58</v>
+        <v>4.02</v>
       </c>
       <c r="N110" t="n">
-        <v>3.33</v>
+        <v>4.98</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M111" t="n">
-        <v>4.47</v>
+        <v>4.63</v>
       </c>
       <c r="N111" t="n">
-        <v>6.91</v>
+        <v>5.54</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB111" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>4.62</v>
+        <v>3.94</v>
       </c>
       <c r="M113" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="N113" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.04</v>
+        <v>8.5</v>
       </c>
       <c r="M114" t="n">
-        <v>3.41</v>
+        <v>5.2</v>
       </c>
       <c r="N114" t="n">
-        <v>3.42</v>
+        <v>1.32</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,16 +14032,16 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M115" t="n">
-        <v>4.27</v>
+        <v>3.48</v>
       </c>
       <c r="N115" t="n">
-        <v>5.33</v>
+        <v>4.78</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.61</v>
+        <v>3.26</v>
       </c>
       <c r="M117" t="n">
-        <v>3.95</v>
+        <v>3.52</v>
       </c>
       <c r="N117" t="n">
-        <v>5.17</v>
+        <v>2.1</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M119" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N119" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.66</v>
+        <v>3.37</v>
       </c>
       <c r="M121" t="n">
-        <v>3.48</v>
+        <v>3.32</v>
       </c>
       <c r="N121" t="n">
-        <v>4.78</v>
+        <v>2.13</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="M125" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N125" t="n">
-        <v>3.54</v>
+        <v>5</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15585,10 +15585,10 @@
         <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,16 +15698,16 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD128" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="M131" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N131" t="n">
-        <v>3.51</v>
+        <v>2.87</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.9</v>
+        <v>1.69</v>
       </c>
       <c r="M132" t="n">
-        <v>3.11</v>
+        <v>4.27</v>
       </c>
       <c r="N132" t="n">
-        <v>2.47</v>
+        <v>5.33</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>8.5</v>
+        <v>1.41</v>
       </c>
       <c r="M133" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="N133" t="n">
-        <v>1.32</v>
+        <v>7.38</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,16 +16293,16 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AC133" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M134" t="n">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N134" t="n">
-        <v>4.74</v>
+        <v>5.17</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="M136" t="n">
-        <v>3.28</v>
+        <v>4.35</v>
       </c>
       <c r="N136" t="n">
-        <v>3.26</v>
+        <v>6.75</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,73 +16724,73 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U137" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V137" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W137" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X137" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD137" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG137" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH137" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI137" s="3" t="n">
         <v>46081.5</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.33</v>
+        <v>3.03</v>
       </c>
       <c r="M140" t="n">
-        <v>4.8</v>
+        <v>3.32</v>
       </c>
       <c r="N140" t="n">
-        <v>8.1</v>
+        <v>2.29</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="M142" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="N142" t="n">
-        <v>3.51</v>
+        <v>3.09</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,22 +17521,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.03</v>
+        <v>2</v>
       </c>
       <c r="M146" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N146" t="n">
-        <v>2.29</v>
+        <v>3.51</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.62</v>
+        <v>1.64</v>
       </c>
       <c r="M148" t="n">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="N148" t="n">
-        <v>2</v>
+        <v>4.74</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,16 +18197,16 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.42</v>
+        <v>3.16</v>
       </c>
       <c r="M150" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="N150" t="n">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,10 +18509,10 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M152" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="N152" t="n">
         <v>5.17</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="M154" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N154" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.84</v>
+        <v>1.54</v>
       </c>
       <c r="M155" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N155" t="n">
-        <v>2.45</v>
+        <v>5.58</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,73 +19104,73 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="M157" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="N157" t="n">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="O157" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V157" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X157" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI157" s="3" t="n">
         <v>46081.5</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="M158" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="N158" t="n">
-        <v>2.88</v>
+        <v>5.57</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="M159" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="N159" t="n">
-        <v>4.67</v>
+        <v>4.28</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.24</v>
+        <v>3.26</v>
       </c>
       <c r="M160" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="N160" t="n">
-        <v>3.09</v>
+        <v>2.22</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,61 +19580,61 @@
         </is>
       </c>
       <c r="L161" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M161" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="N161" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD161" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M161" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N161" t="n">
-        <v>5</v>
-      </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" t="n">
-        <v>0</v>
-      </c>
-      <c r="V161" t="n">
-        <v>0</v>
-      </c>
-      <c r="W161" t="n">
-        <v>0</v>
-      </c>
-      <c r="X161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>0</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>3.26</v>
+        <v>2.04</v>
       </c>
       <c r="M163" t="n">
-        <v>3.22</v>
+        <v>3.41</v>
       </c>
       <c r="N163" t="n">
-        <v>2.22</v>
+        <v>3.42</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>5.53</v>
+        <v>4.62</v>
       </c>
       <c r="M164" t="n">
-        <v>4.39</v>
+        <v>3.88</v>
       </c>
       <c r="N164" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>3.26</v>
+        <v>4.61</v>
       </c>
       <c r="M168" t="n">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="N168" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB168" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="M184" t="n">
-        <v>3.53</v>
+        <v>6.6</v>
       </c>
       <c r="N184" t="n">
-        <v>3.15</v>
+        <v>14.1</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="M190" t="n">
-        <v>2.75</v>
+        <v>3.53</v>
       </c>
       <c r="N190" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB190" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,22 +24661,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 1